--- a/학습리포트_데이터.xlsx
+++ b/학습리포트_데이터.xlsx
@@ -440,7 +440,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2335285197</v>
+        <v>8229980629</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-04</v>
@@ -469,7 +469,7 @@
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>4025970326</v>
+        <v>8786537443</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-07</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>9172964032</v>
+        <v>2318797335</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-11</v>
@@ -528,7 +528,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1483179250</v>
+        <v>2208107553</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-14</v>
@@ -557,7 +557,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1390290307</v>
+        <v>3202304127</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-18</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4937261188</v>
+        <v>3313989314</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-21</v>
@@ -615,7 +615,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1325422150</v>
+        <v>4740615217</v>
       </c>
       <c r="B8" t="str">
         <v>2026-03-25</v>
@@ -644,7 +644,7 @@
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>4771129070</v>
+        <v>7902798942</v>
       </c>
       <c r="B9" t="str">
         <v>2026-04-01</v>
@@ -681,7 +681,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -697,191 +697,9 @@
         <v>상태</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>▼ 2026년 3월 7일 (토)</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>조재환</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-07</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2335285197-과제1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>조재환</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-07</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2335285197-과제2</v>
-      </c>
-      <c r="D4" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>조재환</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-07</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2335285197-과제3</v>
-      </c>
-      <c r="D5" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>▼ 2026년 3월 11일 (수)</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>조재환</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="C7" t="str">
-        <v>4025970326-과제2</v>
-      </c>
-      <c r="D7" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>▼ 2026년 3월 21일 (토)</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>조재환</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C9" t="str">
-        <v>1390290307-과제1</v>
-      </c>
-      <c r="D9" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>▼ 2026년 3월 25일 (수)</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>조재환</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="C11" t="str">
-        <v>4937261188-과제1</v>
-      </c>
-      <c r="D11" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>조재환</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="C12" t="str">
-        <v>4937261188-과제2</v>
-      </c>
-      <c r="D12" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>▼ 2026년 4월 1일 (수)</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>조재환</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="C14" t="str">
-        <v>1325422150-과제1</v>
-      </c>
-      <c r="D14" t="str">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/학습리포트_데이터.xlsx
+++ b/학습리포트_데이터.xlsx
@@ -8,30 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="수업정보" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2026-05-14" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2026-05-16" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2026-05-19" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2026-05-23" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2026-05-26" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2026-05-30" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2026-06-02" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2026-06-06" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="2026-06-09" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="2026-06-13" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="2026-06-16" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="2026-06-20" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="2026-06-23" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="2026-06-27" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="2026-06-30" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="2026-07-04" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="2026-07-07" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="2026-07-11" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="2026-07-14" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="2026-07-18" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="2026-07-21" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="2026-07-25" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="2026-07-28" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="설정" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2026-05-09" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-05-14" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-05-16" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-05-19" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-05-23" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-05-26" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-05-30" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-06-02" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-06-06" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026-06-09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2026-06-13" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="2026-06-16" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2026-06-20" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="2026-06-23" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2026-06-27" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="2026-06-30" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2026-07-04" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="2026-07-07" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2026-07-11" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-07-14" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2026-07-18" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-07-21" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-07-25" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-07-28" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="설정" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,17 +491,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7263135459</t>
+          <t>3316841930</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>풍산자 라이트유형</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>여러가지 방정식</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7. 여러가지 방정식 p.93~102 (유형 01~13)</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -509,17 +522,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1611388089</t>
+          <t>2049300210</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>풍산자 라이트유형</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>여러가지 방정식</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7. 여러가지 방정식 p.103 (유형 14) + 복습</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -528,12 +553,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5109136912</t>
+          <t>3316718333</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -547,12 +572,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5963047327</t>
+          <t>3249007319</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -566,12 +591,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1223242507</t>
+          <t>1622959063</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -585,12 +610,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5475025651</t>
+          <t>8214417619</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -604,12 +629,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1449955060</t>
+          <t>4999154565</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -623,12 +648,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6490958556</t>
+          <t>9306501428</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -642,12 +667,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9847061380</t>
+          <t>8370836915</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -661,12 +686,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2604587035</t>
+          <t>5510554856</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -680,12 +705,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4682943136</t>
+          <t>1850660654</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -699,12 +724,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5139719221</t>
+          <t>1237058955</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -718,12 +743,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7840143239</t>
+          <t>7772264534</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -737,12 +762,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1661150095</t>
+          <t>7297684682</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -756,12 +781,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6820121364</t>
+          <t>8683055667</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -775,12 +800,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7610427382</t>
+          <t>8818487830</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -794,12 +819,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9362259287</t>
+          <t>9577892678</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -813,12 +838,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5979244569</t>
+          <t>9520664107</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -832,12 +857,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6619371869</t>
+          <t>8883155664</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -851,12 +876,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4636898871</t>
+          <t>2239240266</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -870,12 +895,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5340249847</t>
+          <t>8791875152</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -889,12 +914,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6323206182</t>
+          <t>2444228035</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -908,12 +933,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9383607384</t>
+          <t>4622727886</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -923,6 +948,25 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2674956223</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3351,6 +3395,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>출결</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>오답</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>과제이행률</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>과제1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>과제2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>과제3</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>과제4</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>인원빈</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>김도은</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>서윤희</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>유하정</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>이선재</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>김희은</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3388,7 +3583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-14 18:13:22</t>
+          <t>2026-05-14 18:30:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
